--- a/Curso_Comunidades_2017/Aula3.xlsx
+++ b/Curso_Comunidades_2017/Aula3.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="992"/>
+    <workbookView xWindow="6552" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="992"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha original" sheetId="1" r:id="rId1"/>
-    <sheet name="Riq.Margalef" sheetId="2" r:id="rId2"/>
-    <sheet name="Simpson" sheetId="3" r:id="rId3"/>
-    <sheet name="Shannon" sheetId="4" r:id="rId4"/>
+    <sheet name="Plan1" sheetId="5" r:id="rId1"/>
+    <sheet name="Riq.Margalef" sheetId="6" r:id="rId2"/>
+    <sheet name="Simpson" sheetId="7" r:id="rId3"/>
+    <sheet name="Shannon" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511" iterateDelta="1E-4"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="24">
   <si>
     <t>Amostra</t>
   </si>
@@ -72,12 +72,42 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>DMg</t>
+  </si>
+  <si>
+    <t>Pi</t>
+  </si>
+  <si>
+    <t>Pi^2</t>
+  </si>
+  <si>
+    <t>1-D</t>
+  </si>
+  <si>
+    <t>Ln(Pi)</t>
+  </si>
+  <si>
+    <t>Pi*Ln(Pi)</t>
+  </si>
+  <si>
+    <t>H'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -87,6 +117,7 @@
       <charset val="1"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -113,16 +144,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -144,16 +176,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>556200</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>159120</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>545400</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>116200</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>58320</xdr:rowOff>
+      <xdr:rowOff>101554</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -166,8 +198,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="556200" y="1373040"/>
-          <a:ext cx="2417760" cy="549360"/>
+          <a:off x="1295400" y="1485900"/>
+          <a:ext cx="1868800" cy="627334"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -186,16 +218,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>218520</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>29880</xdr:rowOff>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>365400</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>516027</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>7200</xdr:rowOff>
+      <xdr:rowOff>115327</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -208,8 +240,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1027800" y="1243800"/>
-          <a:ext cx="1766160" cy="1278000"/>
+          <a:off x="2164080" y="1424940"/>
+          <a:ext cx="1399947" cy="1433587"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -228,16 +260,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>251280</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114840</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>376200</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>539787</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>29520</xdr:rowOff>
+      <xdr:rowOff>138200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -250,8 +282,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1060560" y="1491480"/>
-          <a:ext cx="1744200" cy="889920"/>
+          <a:off x="1600200" y="1691640"/>
+          <a:ext cx="1377987" cy="1006880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -531,24 +563,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="8.5546875"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="8.5546875"/>
-    <col min="8" max="1024" width="8.5546875"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -562,16 +588,16 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>4</v>
       </c>
       <c r="E2">
@@ -585,16 +611,16 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3">
@@ -608,16 +634,16 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>7</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>4</v>
       </c>
       <c r="E4">
@@ -631,16 +657,16 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>15</v>
       </c>
       <c r="E5">
@@ -654,16 +680,16 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>6</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>4</v>
       </c>
       <c r="E6">
@@ -680,13 +706,13 @@
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>4</v>
       </c>
       <c r="E7">
@@ -700,446 +726,754 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1025" width="9.109375"/>
+    <col min="9" max="9" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>COUNTIF(B2:F2,"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <f>SUM(B2:F2)</f>
+        <v>18</v>
+      </c>
+      <c r="I2" s="4">
+        <f>(G2-1)/LN(H2)</f>
+        <v>0.69195251252238721</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G7" si="0">COUNTIF(B3:F3,"&gt;0")</f>
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H7" si="1">SUM(B3:F3)</f>
+        <v>11</v>
+      </c>
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I7" si="2">(G3-1)/LN(H3)</f>
+        <v>0.41703239142424631</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="2"/>
+        <v>1.0188698156853258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="C5" s="1">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="2"/>
+        <v>0.64703090629734494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>8</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I6" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1078081192065652</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
+      <c r="B7">
         <v>8</v>
       </c>
-      <c r="D7" s="3">
-        <v>4</v>
+      <c r="C7" s="2">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="J7" s="4"/>
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" si="2"/>
+        <v>0.93200240183941774</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1025" width="9.109375"/>
+    <col min="7" max="10" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="G1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <f>COUNTIF(B2:F2,"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="H2" s="3">
+        <f>SUM(B2:F2)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1">
+        <f>B2/$H2</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C3" s="1">
+        <f>C2/$H2</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="D3" s="1">
+        <f>D2/$H2</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E3" s="1">
+        <f>E2/$H2</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <f>F2/$H2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1">
+        <f>B3^2</f>
+        <v>1.2345679012345678E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" ref="C4:F4" si="0">C3^2</f>
+        <v>4.9382716049382713E-2</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <f>SUM(B4:F4)</f>
+        <v>0.50617283950617287</v>
+      </c>
+      <c r="J4" s="3">
+        <f>1-I4</f>
+        <v>0.49382716049382713</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" ref="G5" si="1">COUNTIF(B5:F5,"&gt;0")</f>
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="K2">
+      <c r="H5" s="3">
+        <f t="shared" ref="H5" si="2">SUM(B5:F5)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
+      <c r="B6" s="1">
+        <f>B5/$H5</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <f>C5/$H5</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <f>D5/$H5</f>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E6" s="1">
+        <f>E5/$H5</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <f>F5/$H5</f>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1">
+        <f>B6^2</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" ref="C7:F7" si="3">C6^2</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="3"/>
+        <v>0.52892561983471076</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="3"/>
+        <v>7.4380165289256187E-2</v>
+      </c>
+      <c r="I7" s="3">
+        <f>SUM(B7:F7)</f>
+        <v>0.60330578512396693</v>
+      </c>
+      <c r="J7" s="3">
+        <f>1-I7</f>
+        <v>0.39669421487603307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1025" width="9.109375"/>
+    <col min="7" max="9" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="G1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <f>COUNTIF(B2:F2,"&gt;0")</f>
+        <v>3</v>
+      </c>
+      <c r="H2" s="3">
+        <f>SUM(B2:F2)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1">
+        <f>B2/$H2</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" ref="C3:F3" si="0">C2/$H2</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" si="0"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1">
+        <f>LN(B3)</f>
+        <v>-2.1972245773362196</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" ref="C4:D4" si="1">LN(C3)</f>
+        <v>-1.5040773967762742</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.40546510810816444</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1">
+        <f>B3*B4</f>
+        <v>-0.24413606414846883</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" ref="C5:F5" si="2">C3*C4</f>
+        <v>-0.33423942150583869</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.27031007207210961</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <f>-SUM(B5:F5)</f>
+        <v>0.84868555772641718</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" ref="G6" si="3">COUNTIF(B6:F6,"&gt;0")</f>
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="2"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="H6" s="3">
+        <f t="shared" ref="H6" si="4">SUM(B6:F6)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1">
+        <f>B6/$H6</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" ref="C7" si="5">C6/$H6</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" ref="D7" si="6">D6/$H6</f>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" ref="E7" si="7">E6/$H6</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" ref="F7" si="8">F6/$H6</f>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" ref="D8:F8" si="9">LN(D7)</f>
+        <v>-0.31845373111853459</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="9"/>
+        <v>-1.2992829841302609</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1">
+        <f>B7*B8</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" ref="C9" si="10">C7*C8</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" ref="D9:F9" si="11">D7*D8</f>
+        <v>-0.23160271354075243</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" ref="E9" si="12">E7*E8</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.35434990476279837</v>
+      </c>
+      <c r="I9" s="3">
+        <f>-SUM(B9:F9)</f>
+        <v>0.58595261830355083</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="0" scale="0" firstPageNumber="0" orientation="portrait" usePrinterDefaults="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
-  </headerFooter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>